--- a/data/archive/2026-09-24.xlsx
+++ b/data/archive/2026-09-24.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:25 UTC</t>
+          <t>2026-09-24 17:06 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 16:25 UTC</t>
+          <t>2026-09-24 17:07 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:26 UTC</t>
+          <t>2026-09-24 17:07 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">

--- a/data/archive/2026-09-24.xlsx
+++ b/data/archive/2026-09-24.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Public Sector - New Grad</t>
+          <t>Forward Deployed Software Engineer - US Government</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -595,12 +595,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Kitsap, WA</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -610,27 +610,23 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>4736426005</t>
+          <t>a2e9ab0f-4dd1-4744-92b9-edc7ae393c58</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
+          <t>https://jobs.lever.co/palantir/a2e9ab0f-4dd1-4744-92b9-edc7ae393c58</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -645,7 +641,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 17:06 UTC</t>
+          <t>2026-09-24 21:40 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -667,12 +663,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Performance Tooling and Infrastructure New Grad</t>
+          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -682,7 +678,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>San Francisco, California; New York, New York</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -692,32 +688,28 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>8227399</t>
+          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8227399</t>
+          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -732,7 +724,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 17:07 UTC</t>
+          <t>2026-09-24 21:40 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -746,96 +738,13 @@
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Palantir</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Forward Deployed Software Engineer - US Government</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Kitsap, WA</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>a2e9ab0f-4dd1-4744-92b9-edc7ae393c58</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>lever</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/palantir/a2e9ab0f-4dd1-4744-92b9-edc7ae393c58</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 17:07 UTC</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q4"/>
+  <autoFilter ref="A1:Q3"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -847,7 +756,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
